--- a/sources/table_normalization/xlsx/economy-table119.xlsx
+++ b/sources/table_normalization/xlsx/economy-table119.xlsx
@@ -97,7 +97,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot; &quot;[$£-809]* #,##0.00&quot; &quot;;&quot;-&quot;[$£-809]* #,##0.00&quot; &quot;;&quot; &quot;[$£-809]* &quot;-&quot;??&quot; &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot; &quot;[$£-809]* #,##0.00&quot; &quot;;&quot;-&quot;[$£-809]* #,##0.00&quot; &quot;;&quot; &quot;[$£-809]* &quot;-&quot;??&quot; &quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -142,18 +142,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -315,36 +309,36 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,7 +825,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -841,13 +835,13 @@
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="15"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4">
@@ -855,7 +849,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6">
@@ -863,7 +857,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6">
@@ -871,7 +865,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="7">
@@ -879,7 +873,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="7">
@@ -887,7 +881,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="8">
@@ -895,7 +889,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="8">
@@ -907,13 +901,13 @@
       <c r="B11" s="9"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="10">
@@ -921,7 +915,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="8">
@@ -929,7 +923,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="8">
@@ -941,10 +935,10 @@
       <c r="B16" s="11"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="17"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
